--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-service-event.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3028" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -942,6 +942,12 @@
   </si>
   <si>
     <t>ServiceEvent.performer.assignedEntity.code.translation</t>
+  </si>
+  <si>
+    <t>ServiceEvent.performer.assignedEntity.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>ServiceEvent.performer.assignedEntity.addr</t>
@@ -1317,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK94"/>
+  <dimension ref="A1:AK95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.05078125" customWidth="true" bestFit="true"/>
@@ -10372,11 +10378,9 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10427,7 +10431,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10447,10 +10451,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10473,10 +10477,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10528,7 +10532,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10548,10 +10552,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10562,7 +10566,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>74</v>
@@ -10574,10 +10578,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -10629,13 +10633,13 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>74</v>
@@ -10649,10 +10653,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10675,10 +10679,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -10730,7 +10734,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10750,10 +10754,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10764,7 +10768,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -10776,9 +10780,11 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="L93" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10829,7 +10835,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10849,10 +10855,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10860,10 +10866,10 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -10875,7 +10881,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>95</v>
+        <v>313</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10931,7 +10937,7 @@
         <v>314</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>75</v>
@@ -10943,6 +10949,105 @@
         <v>74</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK95" t="s" s="2">
         <v>74</v>
       </c>
     </row>
